--- a/10_Trade_Finance/_template_TRADE_FINANCE.xlsx
+++ b/10_Trade_Finance/_template_TRADE_FINANCE.xlsx
@@ -386,88 +386,92 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -726,46 +730,46 @@
   <dimension ref="B2:C7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -788,111 +792,111 @@
   <dimension ref="B2:D16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="7" t="str">
+      <c r="C12" s="8" t="str">
         <f aca="false">IFERROR(C7/C5*365,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="str">
+      <c r="C13" s="8" t="str">
         <f aca="false">IFERROR(C8/C6*365,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="7" t="str">
+      <c r="C14" s="8" t="str">
         <f aca="false">IFERROR(C9/C6*365,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="8" t="str">
+      <c r="C15" s="9" t="str">
         <f aca="false">IFERROR(C12+C13-C14,"-")</f>
         <v>-</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="10" t="str">
+      <c r="C16" s="11" t="str">
         <f aca="false">IFERROR(C15/365*C6,"-")</f>
         <v>-</v>
       </c>
@@ -916,145 +920,145 @@
   <dimension ref="B2:D21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">C5*(C6+C7)*(C8/365)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="14" t="str">
+      <c r="C10" s="15" t="str">
         <f aca="false">IFERROR(C9/C5/(C8/365),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>0.85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="13" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="11" t="n">
         <f aca="false">C14*C15</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="11" t="n">
         <f aca="false">C14*C16</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="11" t="n">
         <f aca="false">C14-C19</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <f aca="false">IFERROR(C16/(C17/365),"-")</f>
         <v>0.121666666666667</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1077,142 +1081,142 @@
   <dimension ref="B2:D20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <f aca="false">C7*C8</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="14" t="str">
+      <c r="C11" s="15" t="str">
         <f aca="false">IFERROR((C9+C10)/C5,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="18" t="str">
+      <c r="C15" s="19" t="str">
         <f aca="false">'LC &amp; Factoring Cost'!C10</f>
         <v>-</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <f aca="false">'LC &amp; Factoring Cost'!C21</f>
         <v>0.121666666666667</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="18" t="str">
+      <c r="C17" s="19" t="str">
         <f aca="false">C11</f>
         <v>-</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="19" t="str">
+      <c r="C19" s="20" t="str">
         <f aca="false">IF(COUNT(C15:C17)&lt;3,"-",INDEX(B15:B17,MATCH(MIN(C15:C17),C15:C17,0)))</f>
         <v>-</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="15" t="str">
+      <c r="C20" s="16" t="str">
         <f aca="false">IF(COUNT(C15:C17)&lt;3,"-",MIN(C15:C17))</f>
         <v>-</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1235,104 +1239,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/10_Trade_Finance/_template_TRADE_FINANCE.xlsx
+++ b/10_Trade_Finance/_template_TRADE_FINANCE.xlsx
@@ -11,8 +11,11 @@
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Working Capital Cycle" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="LC &amp; Factoring Cost" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Financing Cost Comparison" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Dynamic Discounting &amp; SCF" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Financing Cost Comparison" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Sources" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Checks" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RefreshLog" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="117">
   <si>
     <t xml:space="preserve">[COUNTERPARTY] — Trade Finance Model</t>
   </si>
@@ -149,6 +152,54 @@
     <t xml:space="preserve">Compare vs. bank credit line rate to decide financing channel</t>
   </si>
   <si>
+    <t xml:space="preserve">Dynamic Discounting &amp; Supply Chain Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two mechanisms this repo's other trade-finance channels don't cover: the implied APR of a standard early-payment TRADE discount (the classic "2/10 net 30" factoid), and reverse factoring, which prices off the BUYER's stronger credit rather than the supplier's own -- the actual reason supply chain finance programs exist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early-Payment Trade Discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount % (e.g. the "2" in 2/10 net 30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount period (days, the "10")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net due period (days, the "30")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied APR of FORGOING the discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard formula: (discount%/(1-discount%)) x (360/(net days - discount days)) -- the classic corporate-finance textbook convention (360-day year). 2/10 net 30 works out to ~36.7% -- paying on day 30 instead of day 10 is effectively borrowing at that rate for 20 days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply Chain Finance (Reverse Factoring)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyer's (stronger) credit-based discount rate, annual (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days paid early (vs. invoice due date)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCF cost ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCF annualized cost (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier's own standalone factoring rate (from LC &amp; Factoring tab)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCF savings vs. standalone factoring (percentage points)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This gap -- financing off the buyer's credit instead of the supplier's own -- is the entire reason SCF/reverse-factoring programs (Taulia, PrimeRevenue, C2FO, etc.) exist</t>
+  </si>
+  <si>
     <t xml:space="preserve">Which Financing Channel Is Cheapest?</t>
   </si>
   <si>
@@ -194,16 +245,121 @@
     <t xml:space="preserve">Revolving credit line</t>
   </si>
   <si>
+    <t xml:space="preserve">Early-payment discount forgone (opportunity cost of not paying early)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supply chain finance (reverse factoring)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cheapest channel</t>
   </si>
   <si>
-    <t xml:space="preserve">Only declares a winner once all three channels have real numbers — one live rate shouldn't beat two blanks by default</t>
+    <t xml:space="preserve">Only declares a winner once all five channels have real numbers — one live rate shouldn't beat four blanks by default</t>
   </si>
   <si>
     <t xml:space="preserve">Cheapest annualized cost %</t>
   </si>
   <si>
-    <t xml:space="preserve">Compares only financing cost — also weigh speed, collateral/covenant burden, and counterparty credit risk transfer (LC shifts payment risk to the issuing bank; factoring can be non-recourse)</t>
+    <t xml:space="preserve">Compares only financing cost — also weigh speed, collateral/covenant burden, and counterparty credit risk transfer (LC shifts payment risk to the issuing bank; factoring can be non-recourse; SCF depends on the buyer maintaining its own credit quality)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early-payment discount implied APR: (d/(1-d)) x (365/(net-discount days))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic corporate-finance working-capital formula (the "2/10 net 30" factoid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes the discount is genuinely available and the buyer has the cash to take it -- otherwise this is a hypothetical cost, not cash actually at risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse factoring priced off the buyer's credit rating, not the supplier's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard supply-chain-finance program mechanics (Taulia, PrimeRevenue, C2FO and similar platforms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires the buyer to sponsor/anchor the program -- not available to a supplier unilaterally the way standalone factoring is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash conversion cycle (DSO+DIO-DPO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard working-capital-cycle definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses average balance-sheet figures, not a true days-weighted transaction-level calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing-cost-only channel comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This model's own explicit framing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling choice, stated directly on the sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliberately ignores speed, collateral/covenant burden, and credit-risk transfer differences between channels -- noted directly rather than silently assumed away</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/10 net 30 reproduces the commonly cited ~37% APR benchmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE at the default 2/10 net 30 terms -- confirms the formula reproduces the textbook figure, not just internally consistent arithmetic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCF is cheaper than the supplier's own standalone factoring whenever the buyer's credit is genuinely stronger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE -- the entire premise of reverse factoring only holds when the buyer's rate really is lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheapest-channel comparison never declares a winner on partial data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LC total cost ties: issuance+confirmation fee x face x (tenor/365) = annualized cost x face x (tenor/365)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) once LC inputs are populated</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -228,13 +384,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -296,16 +453,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF008000"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -386,7 +543,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -459,15 +616,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1078,13 +1259,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:D18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1092,132 +1273,118 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="5" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="17" t="n">
-        <v>0.005</v>
+      <c r="C7" s="13" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
+      <c r="C8" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <f aca="false">C5*C6</f>
+      <c r="C9" s="18" t="n">
+        <f aca="false">IFERROR((C6/(1-C6))*(360/(C8-C7)),"-")</f>
+        <v>0.36734693877551</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <f aca="false">C7*C8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="15" t="str">
-        <f aca="false">IFERROR((C9+C10)/C5,"-")</f>
-        <v>-</v>
-      </c>
-    </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="C13" s="17" t="n">
+        <v>0.045</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>52</v>
+      <c r="C14" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="19" t="str">
-        <f aca="false">'LC &amp; Factoring Cost'!C10</f>
-        <v>-</v>
+        <v>52</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <f aca="false">C12*C13*(C14/365)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <f aca="false">C13</f>
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C17" s="20" t="n">
         <f aca="false">'LC &amp; Factoring Cost'!C21</f>
         <v>0.121666666666667</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="19" t="str">
-        <f aca="false">C11</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+      <c r="C18" s="19" t="n">
+        <f aca="false">IFERROR(C17-C16,"-")</f>
+        <v>0.0766666666666667</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="C19" s="20" t="str">
-        <f aca="false">IF(COUNT(C15:C17)&lt;3,"-",INDEX(B15:B17,MATCH(MIN(C15:C17),C15:C17,0)))</f>
-        <v>-</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="16" t="str">
-        <f aca="false">IF(COUNT(C15:C17)&lt;3,"-",MIN(C15:C17))</f>
-        <v>-</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1236,6 +1403,382 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:D22"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <f aca="false">C5*C6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <f aca="false">C7*C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="15" t="str">
+        <f aca="false">IFERROR((C9+C10)/C5,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="22" t="str">
+        <f aca="false">'LC &amp; Factoring Cost'!C10</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <f aca="false">'LC &amp; Factoring Cost'!C21</f>
+        <v>0.121666666666667</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="22" t="str">
+        <f aca="false">C11</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <f aca="false">'Dynamic Discounting &amp; SCF'!C9</f>
+        <v>0.36734693877551</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <f aca="false">'Dynamic Discounting &amp; SCF'!C16</f>
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="23" t="str">
+        <f aca="false">IF(COUNT(C15:C19)&lt;5,"-",INDEX(B15:B19,MATCH(MIN(C15:C19),C15:C19,0)))</f>
+        <v>-</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="16" t="str">
+        <f aca="false">IF(COUNT(C15:C19)&lt;5,"-",MIN(C15:C19))</f>
+        <v>-</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="26" t="b">
+        <f aca="false">IF(AND('Dynamic Discounting &amp; SCF'!C6=0.02,'Dynamic Discounting &amp; SCF'!C7=10,'Dynamic Discounting &amp; SCF'!C8=30),ABS('Dynamic Discounting &amp; SCF'!C9-0.3673)&lt;0.001,TRUE())</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="26" t="b">
+        <f aca="false">IF('Dynamic Discounting &amp; SCF'!C13&lt;'Dynamic Discounting &amp; SCF'!C17,'Dynamic Discounting &amp; SCF'!C18&gt;0,TRUE())</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="26" t="b">
+        <f aca="false">IF(COUNT('Financing Cost Comparison'!C15:C19)&lt;5,'Financing Cost Comparison'!C21="-",TRUE())</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="23" t="str">
+        <f aca="false">IFERROR('LC &amp; Factoring Cost'!C9-'LC &amp; Factoring Cost'!C10*'LC &amp; Factoring Cost'!C5*('LC &amp; Factoring Cost'!C8/365),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1248,95 +1791,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>65</v>
+      <c r="B4" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
